--- a/cet4/result/10_重生科技_女学霸的商业帝国/10_重生科技_女学霸的商业帝国_学习版.xlsx
+++ b/cet4/result/10_重生科技_女学霸的商业帝国/10_重生科技_女学霸的商业帝国_学习版.xlsx
@@ -397,731 +397,647 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D45"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>author</v>
       </c>
       <c r="B2" t="str">
-        <v>author</v>
+        <v>/ˈɔːθər/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D2" t="str">
         <v>作者</v>
       </c>
-      <c r="D2" t="str">
-        <v>author(作者)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>AI</v>
       </c>
       <c r="B3" t="str">
-        <v>AI</v>
+        <v>/ˌeɪ ˈaɪ/</v>
       </c>
       <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
         <v>人工智能</v>
       </c>
-      <c r="D3" t="str">
-        <v>AI(人工智能)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>magnetic</v>
       </c>
       <c r="B4" t="str">
-        <v>magnetic</v>
+        <v>/mæɡˈnetɪk/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>磁性的</v>
       </c>
-      <c r="D4" t="str">
-        <v>magnetic(磁性的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>precision</v>
       </c>
       <c r="B5" t="str">
-        <v>precision</v>
+        <v>/prɪˈsɪʒn/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>精度</v>
       </c>
-      <c r="D5" t="str">
-        <v>precision(精度)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>compare</v>
       </c>
       <c r="B6" t="str">
-        <v>compare</v>
+        <v>/kəmˈper/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D6" t="str">
         <v>比较</v>
       </c>
-      <c r="D6" t="str">
-        <v>compare(比较)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>way</v>
       </c>
       <c r="B7" t="str">
-        <v>way</v>
+        <v>/weɪ/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>道路</v>
       </c>
-      <c r="D7" t="str">
-        <v>way(道路)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>struggle</v>
       </c>
       <c r="B8" t="str">
-        <v>struggle</v>
+        <v>/ˈstrʌɡl/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>奋斗</v>
       </c>
-      <c r="D8" t="str">
-        <v>struggle(奋斗)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>pronunciation</v>
       </c>
       <c r="B9" t="str">
-        <v>pronunciation</v>
+        <v>/prəˌnʌnsiˈeɪʃn/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>发音</v>
       </c>
-      <c r="D9" t="str">
-        <v>pronunciation(发音)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>awfully</v>
       </c>
       <c r="B10" t="str">
-        <v>awfully</v>
+        <v>/ˈɔːfli/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D10" t="str">
         <v>非常</v>
       </c>
-      <c r="D10" t="str">
-        <v>awfully(非常)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>summarize</v>
       </c>
       <c r="B11" t="str">
-        <v>summarize</v>
+        <v>/ˈsʌməraɪz/</v>
       </c>
       <c r="C11" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>总结</v>
       </c>
-      <c r="D11" t="str">
-        <v>summarize(总结)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>artistic</v>
       </c>
       <c r="B12" t="str">
-        <v>artistic</v>
+        <v>/ɑːrˈtɪstɪk/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>艺术的</v>
       </c>
-      <c r="D12" t="str">
-        <v>artistic(艺术的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>you</v>
       </c>
       <c r="B13" t="str">
-        <v>you</v>
+        <v>/jə,juː/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D13" t="str">
         <v>你</v>
       </c>
-      <c r="D13" t="str">
-        <v>you(你)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>sufficiently</v>
       </c>
       <c r="B14" t="str">
-        <v>sufficiently</v>
+        <v>/səˈfɪʃntli/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D14" t="str">
         <v>足够地</v>
       </c>
-      <c r="D14" t="str">
-        <v>sufficiently(足够地)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>wireless</v>
       </c>
       <c r="B15" t="str">
-        <v>wireless</v>
+        <v>/ˈwaɪərləs/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>无线的</v>
       </c>
-      <c r="D15" t="str">
-        <v>wireless(无线的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>continual</v>
       </c>
       <c r="B16" t="str">
-        <v>continual</v>
+        <v>/kənˈtɪnjuəl/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>持续的</v>
       </c>
-      <c r="D16" t="str">
-        <v>continual(持续的)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>tender</v>
       </c>
       <c r="B17" t="str">
-        <v>tender</v>
+        <v>/ˈtendər/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>敏感的</v>
       </c>
-      <c r="D17" t="str">
-        <v>tender(敏感的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>torch</v>
       </c>
       <c r="B18" t="str">
-        <v>torch</v>
+        <v>/tɔːrtʃ/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>手电筒</v>
       </c>
-      <c r="D18" t="str">
-        <v>torch(手电筒)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>tray</v>
       </c>
       <c r="B19" t="str">
-        <v>tray</v>
+        <v>/treɪ/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>托盘</v>
       </c>
-      <c r="D19" t="str">
-        <v>tray(托盘)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>mixture</v>
       </c>
       <c r="B20" t="str">
-        <v>tender</v>
+        <v>/ˈmɪkstʃər/</v>
       </c>
       <c r="C20" t="str">
-        <v>温柔的</v>
+        <v>n.</v>
       </c>
       <c r="D20" t="str">
-        <v>tender(温柔的)📢</v>
+        <v>混合物</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>ratio</v>
       </c>
       <c r="B21" t="str">
-        <v>mixture</v>
+        <v>/ˈreɪʃioʊ/</v>
       </c>
       <c r="C21" t="str">
-        <v>混合物</v>
+        <v>n.</v>
       </c>
       <c r="D21" t="str">
-        <v>mixture(混合物)📢</v>
+        <v>比例</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>accuse</v>
       </c>
       <c r="B22" t="str">
-        <v>ratio</v>
+        <v>/əˈkjuːz/</v>
       </c>
       <c r="C22" t="str">
-        <v>比例</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D22" t="str">
-        <v>ratio(比例)📢</v>
+        <v>指控</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>miserable</v>
       </c>
       <c r="B23" t="str">
-        <v>accuse</v>
+        <v>/ˈmɪzrəbl/</v>
       </c>
       <c r="C23" t="str">
-        <v>指控</v>
+        <v>adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>accuse(指控)📢</v>
+        <v>悲惨的</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>omit</v>
       </c>
       <c r="B24" t="str">
-        <v>miserable</v>
+        <v>/əˈmɪt/</v>
       </c>
       <c r="C24" t="str">
-        <v>悲惨的</v>
+        <v>vt.</v>
       </c>
       <c r="D24" t="str">
-        <v>miserable(悲惨的)📢</v>
+        <v>省略</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>multiply</v>
       </c>
       <c r="B25" t="str">
-        <v>omit</v>
+        <v>/ˈmʌltɪplaɪ/</v>
       </c>
       <c r="C25" t="str">
-        <v>省略</v>
+        <v>vt./vi./v./adj./adv.</v>
       </c>
       <c r="D25" t="str">
-        <v>omit(省略)📢</v>
+        <v>增加</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>request</v>
       </c>
       <c r="B26" t="str">
-        <v>multiply</v>
+        <v>/rɪˈkwest/</v>
       </c>
       <c r="C26" t="str">
-        <v>增加</v>
+        <v>n./vt.</v>
       </c>
       <c r="D26" t="str">
-        <v>multiply(增加)📢</v>
+        <v>请求</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>north</v>
       </c>
       <c r="B27" t="str">
-        <v>request</v>
+        <v>/nɔːrθ/</v>
       </c>
       <c r="C27" t="str">
-        <v>请求</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D27" t="str">
-        <v>request(请求)📢</v>
+        <v>北方</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>craft</v>
       </c>
       <c r="B28" t="str">
-        <v>north</v>
+        <v>/kræft/</v>
       </c>
       <c r="C28" t="str">
-        <v>北方</v>
+        <v>n./vt.</v>
       </c>
       <c r="D28" t="str">
-        <v>north(北方)📢</v>
+        <v>工艺</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>quantity</v>
       </c>
       <c r="B29" t="str">
-        <v>craft</v>
+        <v>/ˈkwɑːntəti/</v>
       </c>
       <c r="C29" t="str">
-        <v>工艺</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>craft(工艺)📢</v>
+        <v>数量</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>Oceania</v>
       </c>
       <c r="B30" t="str">
-        <v>quantity</v>
+        <v>/ˌoʊʃiˈɑːniə/</v>
       </c>
       <c r="C30" t="str">
-        <v>数量</v>
+        <v>n.</v>
       </c>
       <c r="D30" t="str">
-        <v>quantity(数量)📢</v>
+        <v>大洋洲</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>volcano</v>
       </c>
       <c r="B31" t="str">
-        <v>Oceania</v>
+        <v>/vɑːlˈkeɪnoʊ/</v>
       </c>
       <c r="C31" t="str">
-        <v>大洋洲</v>
+        <v>n.</v>
       </c>
       <c r="D31" t="str">
-        <v>Oceania(大洋洲)📢</v>
+        <v>火山</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>rule</v>
       </c>
       <c r="B32" t="str">
-        <v>volcano</v>
+        <v>/ruːl/</v>
       </c>
       <c r="C32" t="str">
-        <v>火山</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>volcano(火山)📢</v>
+        <v>规则</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>scold</v>
       </c>
       <c r="B33" t="str">
-        <v>rule</v>
+        <v>/skoʊld/</v>
       </c>
       <c r="C33" t="str">
-        <v>规则</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>rule(规则)📢</v>
+        <v>责骂</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>shore</v>
       </c>
       <c r="B34" t="str">
-        <v>scold</v>
+        <v>/ʃɔːr/</v>
       </c>
       <c r="C34" t="str">
-        <v>责骂</v>
+        <v>n./v.</v>
       </c>
       <c r="D34" t="str">
-        <v>scold(责骂)📢</v>
+        <v>海岸</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>sparkle</v>
       </c>
       <c r="B35" t="str">
-        <v>shore</v>
+        <v>/ˈspɑːrkl/</v>
       </c>
       <c r="C35" t="str">
-        <v>海岸</v>
+        <v>n./v.</v>
       </c>
       <c r="D35" t="str">
-        <v>shore(海岸)📢</v>
+        <v>闪耀</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>puppet</v>
       </c>
       <c r="B36" t="str">
-        <v>sparkle</v>
+        <v>/ˈpʌpɪt/</v>
       </c>
       <c r="C36" t="str">
-        <v>闪耀</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>sparkle(闪耀)📢</v>
+        <v>傀儡</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>nerve</v>
       </c>
       <c r="B37" t="str">
-        <v>you</v>
+        <v>/nɜːrv/</v>
       </c>
       <c r="C37" t="str">
-        <v>你</v>
+        <v>n./vt.</v>
       </c>
       <c r="D37" t="str">
-        <v>you(你)📢</v>
+        <v>勇气</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>withstand</v>
       </c>
       <c r="B38" t="str">
-        <v>puppet</v>
+        <v>/wɪθˈstænd/</v>
       </c>
       <c r="C38" t="str">
-        <v>傀儡</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>puppet(傀儡)📢</v>
+        <v>抵抗</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>promise</v>
       </c>
       <c r="B39" t="str">
-        <v>continual</v>
+        <v>/ˈprɑːmɪs/</v>
       </c>
       <c r="C39" t="str">
-        <v>持续不断的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>continual(持续不断的)📢</v>
+        <v>承诺</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>lion</v>
       </c>
       <c r="B40" t="str">
-        <v>volcano</v>
+        <v>/ˈlaɪən/</v>
       </c>
       <c r="C40" t="str">
-        <v>火山</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>volcano(火山)📢</v>
+        <v>狮子</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>sight</v>
       </c>
       <c r="B41" t="str">
-        <v>nerve</v>
+        <v>/saɪt/</v>
       </c>
       <c r="C41" t="str">
-        <v>勇气</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>nerve(勇气)📢</v>
+        <v>景象</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>mask</v>
       </c>
       <c r="B42" t="str">
-        <v>precision</v>
+        <v>/mæsk/</v>
       </c>
       <c r="C42" t="str">
-        <v>精确度</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>precision(精确度)📢</v>
+        <v>面具</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>strap</v>
       </c>
       <c r="B43" t="str">
-        <v>withstand</v>
+        <v>/stræp/</v>
       </c>
       <c r="C43" t="str">
-        <v>抵抗</v>
+        <v>n./v.</v>
       </c>
       <c r="D43" t="str">
-        <v>withstand(抵抗)📢</v>
+        <v>带子</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>bush</v>
       </c>
       <c r="B44" t="str">
-        <v>promise</v>
+        <v>/bʊʃ/</v>
       </c>
       <c r="C44" t="str">
-        <v>承诺</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D44" t="str">
-        <v>promise(承诺)📢</v>
+        <v>灌木丛</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>fortune</v>
       </c>
       <c r="B45" t="str">
-        <v>lion</v>
+        <v>/ˈfɔːrtʃən/</v>
       </c>
       <c r="C45" t="str">
-        <v>狮子</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>lion(狮子)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>sight</v>
-      </c>
-      <c r="C46" t="str">
-        <v>景象</v>
-      </c>
-      <c r="D46" t="str">
-        <v>sight(景象)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>mask</v>
-      </c>
-      <c r="C47" t="str">
-        <v>面具</v>
-      </c>
-      <c r="D47" t="str">
-        <v>mask(面具)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>strap</v>
-      </c>
-      <c r="C48" t="str">
-        <v>带子</v>
-      </c>
-      <c r="D48" t="str">
-        <v>strap(带子)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>tender</v>
-      </c>
-      <c r="C49" t="str">
-        <v>温柔的</v>
-      </c>
-      <c r="D49" t="str">
-        <v>tender(温柔的)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>bush</v>
-      </c>
-      <c r="C50" t="str">
-        <v>灌木丛</v>
-      </c>
-      <c r="D50" t="str">
-        <v>bush(灌木丛)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>fortune</v>
-      </c>
-      <c r="C51" t="str">
         <v>财富</v>
-      </c>
-      <c r="D51" t="str">
-        <v>fortune(财富)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
   </ignoredErrors>
 </worksheet>
 </file>